--- a/registration_forms/043_martial_arts_registration_and_liability_waiver_form--registration_forms.xlsx
+++ b/registration_forms/043_martial_arts_registration_and_liability_waiver_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_"i,_the_undersigned,_hereby_give_permission_to_the_martial_arts_school_to_use_my_child's_name_and_contact_information_for_administrative_and_marketing_purposes",_'value':_"i,_the_undersigned,_hereby_give_permission_to_the_martial_arts_school_to_use_my_child's_name_and_contact_information_for_administrative_and_marketing_purposes"}</t>
+          <t>i,_the_undersigned,_hereby_give_permission_to_the_martial_arts_school_to_use_my_child's_name_and_contact_information_for_administrative_and_marketing_purposes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': "I, the undersigned, hereby give permission to the martial arts school to use my child's name and contact information for administrative and marketing purposes", 'value': "I, the undersigned, hereby give permission to the martial arts school to use my child's name and contact information for administrative and marketing purposes"}</t>
+          <t>I, the undersigned, hereby give permission to the martial arts school to use my child's name and contact information for administrative and marketing purposes</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
